--- a/figures/lecture5/6345.0/63450table2ato9a.xlsx
+++ b/figures/lecture5/6345.0/63450table2ato9a.xlsx
@@ -17,386 +17,386 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2704282J">Data1!$M$1:$M$10,Data1!$M$11:$M$36</definedName>
-    <definedName name="A2704282J_Data">Data1!$M$11:$M$36</definedName>
-    <definedName name="A2704282J_Latest">Data1!$M$36</definedName>
-    <definedName name="A2704396F">Data1!$E$1:$E$10,Data1!$E$11:$E$36</definedName>
-    <definedName name="A2704396F_Data">Data1!$E$11:$E$36</definedName>
-    <definedName name="A2704396F_Latest">Data1!$E$36</definedName>
-    <definedName name="A2704472W">Data1!$U$1:$U$10,Data1!$U$11:$U$36</definedName>
-    <definedName name="A2704472W_Data">Data1!$U$11:$U$36</definedName>
-    <definedName name="A2704472W_Latest">Data1!$U$36</definedName>
-    <definedName name="A2704548F">Data1!$O$1:$O$10,Data1!$O$11:$O$36</definedName>
-    <definedName name="A2704548F_Data">Data1!$O$11:$O$36</definedName>
-    <definedName name="A2704548F_Latest">Data1!$O$36</definedName>
-    <definedName name="A2704662K">Data1!$G$1:$G$10,Data1!$G$11:$G$36</definedName>
-    <definedName name="A2704662K_Data">Data1!$G$11:$G$36</definedName>
-    <definedName name="A2704662K_Latest">Data1!$G$36</definedName>
-    <definedName name="A2704738V">Data1!$W$1:$W$10,Data1!$W$11:$W$36</definedName>
-    <definedName name="A2704738V_Data">Data1!$W$11:$W$36</definedName>
-    <definedName name="A2704738V_Latest">Data1!$W$36</definedName>
-    <definedName name="A2704814K">Data1!$R$1:$R$10,Data1!$R$11:$R$36</definedName>
-    <definedName name="A2704814K_Data">Data1!$R$11:$R$36</definedName>
-    <definedName name="A2704814K_Latest">Data1!$R$36</definedName>
-    <definedName name="A2704928J">Data1!$J$1:$J$10,Data1!$J$11:$J$36</definedName>
-    <definedName name="A2704928J_Data">Data1!$J$11:$J$36</definedName>
-    <definedName name="A2704928J_Latest">Data1!$J$36</definedName>
-    <definedName name="A2705004A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$36</definedName>
-    <definedName name="A2705004A_Data">Data1!$Z$11:$Z$36</definedName>
-    <definedName name="A2705004A_Latest">Data1!$Z$36</definedName>
-    <definedName name="A2705044V">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$36</definedName>
-    <definedName name="A2705044V_Data">Data1!$AS$11:$AS$36</definedName>
-    <definedName name="A2705044V_Latest">Data1!$AS$36</definedName>
-    <definedName name="A2705046X">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$36</definedName>
-    <definedName name="A2705046X_Data">Data1!$AI$11:$AI$36</definedName>
-    <definedName name="A2705046X_Latest">Data1!$AI$36</definedName>
-    <definedName name="A2705048C">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$36</definedName>
-    <definedName name="A2705048C_Data">Data1!$AQ$11:$AQ$36</definedName>
-    <definedName name="A2705048C_Latest">Data1!$AQ$36</definedName>
-    <definedName name="A2705050R">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$36</definedName>
-    <definedName name="A2705050R_Data">Data1!$AL$11:$AL$36</definedName>
-    <definedName name="A2705050R_Latest">Data1!$AL$36</definedName>
-    <definedName name="A2705052V">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$36</definedName>
-    <definedName name="A2705052V_Data">Data1!$AJ$11:$AJ$36</definedName>
-    <definedName name="A2705052V_Latest">Data1!$AJ$36</definedName>
-    <definedName name="A2705054X">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$36</definedName>
-    <definedName name="A2705054X_Data">Data1!$AN$11:$AN$36</definedName>
-    <definedName name="A2705054X_Latest">Data1!$AN$36</definedName>
-    <definedName name="A2705056C">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$36</definedName>
-    <definedName name="A2705056C_Data">Data1!$AE$11:$AE$36</definedName>
-    <definedName name="A2705056C_Latest">Data1!$AE$36</definedName>
-    <definedName name="A2705058J">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$36</definedName>
-    <definedName name="A2705058J_Data">Data1!$AR$11:$AR$36</definedName>
-    <definedName name="A2705058J_Latest">Data1!$AR$36</definedName>
-    <definedName name="A2705060V">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$36</definedName>
-    <definedName name="A2705060V_Data">Data1!$AC$11:$AC$36</definedName>
-    <definedName name="A2705060V_Latest">Data1!$AC$36</definedName>
-    <definedName name="A2705062X">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$36</definedName>
-    <definedName name="A2705062X_Data">Data1!$AK$11:$AK$36</definedName>
-    <definedName name="A2705062X_Latest">Data1!$AK$36</definedName>
-    <definedName name="A2705064C">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$36</definedName>
-    <definedName name="A2705064C_Data">Data1!$AD$11:$AD$36</definedName>
-    <definedName name="A2705064C_Latest">Data1!$AD$36</definedName>
-    <definedName name="A2705066J">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$36</definedName>
-    <definedName name="A2705066J_Data">Data1!$AO$11:$AO$36</definedName>
-    <definedName name="A2705066J_Latest">Data1!$AO$36</definedName>
-    <definedName name="A2705068L">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$36</definedName>
-    <definedName name="A2705068L_Data">Data1!$AP$11:$AP$36</definedName>
-    <definedName name="A2705068L_Latest">Data1!$AP$36</definedName>
-    <definedName name="A2705070X">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$36</definedName>
-    <definedName name="A2705070X_Data">Data1!$AH$11:$AH$36</definedName>
-    <definedName name="A2705070X_Latest">Data1!$AH$36</definedName>
-    <definedName name="A2705072C">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$36</definedName>
-    <definedName name="A2705072C_Data">Data1!$AG$11:$AG$36</definedName>
-    <definedName name="A2705072C_Latest">Data1!$AG$36</definedName>
-    <definedName name="A2705074J">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$36</definedName>
-    <definedName name="A2705074J_Data">Data1!$AT$11:$AT$36</definedName>
-    <definedName name="A2705074J_Latest">Data1!$AT$36</definedName>
-    <definedName name="A2705076L">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$36</definedName>
-    <definedName name="A2705076L_Data">Data1!$AF$11:$AF$36</definedName>
-    <definedName name="A2705076L_Latest">Data1!$AF$36</definedName>
-    <definedName name="A2705078T">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$36</definedName>
-    <definedName name="A2705078T_Data">Data1!$AM$11:$AM$36</definedName>
-    <definedName name="A2705078T_Latest">Data1!$AM$36</definedName>
-    <definedName name="A2705080C">Data1!$B$1:$B$10,Data1!$B$11:$B$36</definedName>
-    <definedName name="A2705080C_Data">Data1!$B$11:$B$36</definedName>
-    <definedName name="A2705080C_Latest">Data1!$B$36</definedName>
-    <definedName name="A2705158T">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$36</definedName>
-    <definedName name="A2705158T_Data">Data1!$BP$11:$BP$36</definedName>
-    <definedName name="A2705158T_Latest">Data1!$BP$36</definedName>
-    <definedName name="A2705160C">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$36</definedName>
-    <definedName name="A2705160C_Data">Data1!$BF$11:$BF$36</definedName>
-    <definedName name="A2705160C_Latest">Data1!$BF$36</definedName>
-    <definedName name="A2705162J">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$36</definedName>
-    <definedName name="A2705162J_Data">Data1!$BN$11:$BN$36</definedName>
-    <definedName name="A2705162J_Latest">Data1!$BN$36</definedName>
-    <definedName name="A2705164L">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$36</definedName>
-    <definedName name="A2705164L_Data">Data1!$BI$11:$BI$36</definedName>
-    <definedName name="A2705164L_Latest">Data1!$BI$36</definedName>
-    <definedName name="A2705166T">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$36</definedName>
-    <definedName name="A2705166T_Data">Data1!$BG$11:$BG$36</definedName>
-    <definedName name="A2705166T_Latest">Data1!$BG$36</definedName>
-    <definedName name="A2705168W">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$36</definedName>
-    <definedName name="A2705168W_Data">Data1!$BK$11:$BK$36</definedName>
-    <definedName name="A2705168W_Latest">Data1!$BK$36</definedName>
-    <definedName name="A2705170J">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$36</definedName>
-    <definedName name="A2705170J_Data">Data1!$BB$11:$BB$36</definedName>
-    <definedName name="A2705170J_Latest">Data1!$BB$36</definedName>
-    <definedName name="A2705172L">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$36</definedName>
-    <definedName name="A2705172L_Data">Data1!$BO$11:$BO$36</definedName>
-    <definedName name="A2705172L_Latest">Data1!$BO$36</definedName>
-    <definedName name="A2705174T">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$36</definedName>
-    <definedName name="A2705174T_Data">Data1!$AZ$11:$AZ$36</definedName>
-    <definedName name="A2705174T_Latest">Data1!$AZ$36</definedName>
-    <definedName name="A2705176W">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$36</definedName>
-    <definedName name="A2705176W_Data">Data1!$BH$11:$BH$36</definedName>
-    <definedName name="A2705176W_Latest">Data1!$BH$36</definedName>
-    <definedName name="A2705178A">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$36</definedName>
-    <definedName name="A2705178A_Data">Data1!$BA$11:$BA$36</definedName>
-    <definedName name="A2705178A_Latest">Data1!$BA$36</definedName>
-    <definedName name="A2705180L">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$36</definedName>
-    <definedName name="A2705180L_Data">Data1!$BL$11:$BL$36</definedName>
-    <definedName name="A2705180L_Latest">Data1!$BL$36</definedName>
-    <definedName name="A2705182T">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$36</definedName>
-    <definedName name="A2705182T_Data">Data1!$BM$11:$BM$36</definedName>
-    <definedName name="A2705182T_Latest">Data1!$BM$36</definedName>
-    <definedName name="A2705184W">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$36</definedName>
-    <definedName name="A2705184W_Data">Data1!$BE$11:$BE$36</definedName>
-    <definedName name="A2705184W_Latest">Data1!$BE$36</definedName>
-    <definedName name="A2705186A">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$36</definedName>
-    <definedName name="A2705186A_Data">Data1!$BD$11:$BD$36</definedName>
-    <definedName name="A2705186A_Latest">Data1!$BD$36</definedName>
-    <definedName name="A2705188F">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$36</definedName>
-    <definedName name="A2705188F_Data">Data1!$BQ$11:$BQ$36</definedName>
-    <definedName name="A2705188F_Latest">Data1!$BQ$36</definedName>
-    <definedName name="A2705190T">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$36</definedName>
-    <definedName name="A2705190T_Data">Data1!$BC$11:$BC$36</definedName>
-    <definedName name="A2705190T_Latest">Data1!$BC$36</definedName>
-    <definedName name="A2705192W">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$36</definedName>
-    <definedName name="A2705192W_Data">Data1!$BJ$11:$BJ$36</definedName>
-    <definedName name="A2705192W_Latest">Data1!$BJ$36</definedName>
-    <definedName name="A2705194A">Data1!$D$1:$D$10,Data1!$D$11:$D$36</definedName>
-    <definedName name="A2705194A_Data">Data1!$D$11:$D$36</definedName>
-    <definedName name="A2705194A_Latest">Data1!$D$36</definedName>
-    <definedName name="A2705238T">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$36</definedName>
-    <definedName name="A2705238T_Data">Data1!$AX$11:$AX$36</definedName>
-    <definedName name="A2705238T_Latest">Data1!$AX$36</definedName>
-    <definedName name="A2705244L">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$36</definedName>
-    <definedName name="A2705244L_Data">Data1!$AV$11:$AV$36</definedName>
-    <definedName name="A2705244L_Latest">Data1!$AV$36</definedName>
-    <definedName name="A2705246T">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$36</definedName>
-    <definedName name="A2705246T_Data">Data1!$AU$11:$AU$36</definedName>
-    <definedName name="A2705246T_Latest">Data1!$AU$36</definedName>
-    <definedName name="A2705248W">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$36</definedName>
-    <definedName name="A2705248W_Data">Data1!$AY$11:$AY$36</definedName>
-    <definedName name="A2705248W_Latest">Data1!$AY$36</definedName>
-    <definedName name="A2705258A">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$36</definedName>
-    <definedName name="A2705258A_Data">Data1!$AW$11:$AW$36</definedName>
-    <definedName name="A2705258A_Latest">Data1!$AW$36</definedName>
-    <definedName name="A2705270T">Data1!$C$1:$C$10,Data1!$C$11:$C$36</definedName>
-    <definedName name="A2705270T_Data">Data1!$C$11:$C$36</definedName>
-    <definedName name="A2705270T_Latest">Data1!$C$36</definedName>
-    <definedName name="A2705346A">Data1!$T$1:$T$10,Data1!$T$11:$T$36</definedName>
-    <definedName name="A2705346A_Data">Data1!$T$11:$T$36</definedName>
-    <definedName name="A2705346A_Latest">Data1!$T$36</definedName>
-    <definedName name="A2705460F">Data1!$L$1:$L$10,Data1!$L$11:$L$36</definedName>
-    <definedName name="A2705460F_Data">Data1!$L$11:$L$36</definedName>
-    <definedName name="A2705460F_Latest">Data1!$L$36</definedName>
-    <definedName name="A2705536R">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$36</definedName>
-    <definedName name="A2705536R_Data">Data1!$AB$11:$AB$36</definedName>
-    <definedName name="A2705536R_Latest">Data1!$AB$36</definedName>
-    <definedName name="A2705612F">Data1!$S$1:$S$10,Data1!$S$11:$S$36</definedName>
-    <definedName name="A2705612F_Data">Data1!$S$11:$S$36</definedName>
-    <definedName name="A2705612F_Latest">Data1!$S$36</definedName>
-    <definedName name="A2705726C">Data1!$K$1:$K$10,Data1!$K$11:$K$36</definedName>
-    <definedName name="A2705726C_Data">Data1!$K$11:$K$36</definedName>
-    <definedName name="A2705726C_Latest">Data1!$K$36</definedName>
-    <definedName name="A2705802V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$36</definedName>
-    <definedName name="A2705802V_Data">Data1!$AA$11:$AA$36</definedName>
-    <definedName name="A2705802V_Latest">Data1!$AA$36</definedName>
-    <definedName name="A2705878R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A2705878R_Data">Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A2705878R_Latest">Data1!$Q$36</definedName>
-    <definedName name="A2705992V">Data1!$I$1:$I$10,Data1!$I$11:$I$36</definedName>
-    <definedName name="A2705992V_Data">Data1!$I$11:$I$36</definedName>
-    <definedName name="A2705992V_Latest">Data1!$I$36</definedName>
-    <definedName name="A2706068F">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$36</definedName>
-    <definedName name="A2706068F_Data">Data1!$Y$11:$Y$36</definedName>
-    <definedName name="A2706068F_Latest">Data1!$Y$36</definedName>
-    <definedName name="A2706144W">Data1!$N$1:$N$10,Data1!$N$11:$N$36</definedName>
-    <definedName name="A2706144W_Data">Data1!$N$11:$N$36</definedName>
-    <definedName name="A2706144W_Latest">Data1!$N$36</definedName>
-    <definedName name="A2706258V">Data1!$F$1:$F$10,Data1!$F$11:$F$36</definedName>
-    <definedName name="A2706258V_Data">Data1!$F$11:$F$36</definedName>
-    <definedName name="A2706258V_Latest">Data1!$F$36</definedName>
-    <definedName name="A2706334K">Data1!$V$1:$V$10,Data1!$V$11:$V$36</definedName>
-    <definedName name="A2706334K_Data">Data1!$V$11:$V$36</definedName>
-    <definedName name="A2706334K_Latest">Data1!$V$36</definedName>
-    <definedName name="A2706410A">Data1!$P$1:$P$10,Data1!$P$11:$P$36</definedName>
-    <definedName name="A2706410A_Data">Data1!$P$11:$P$36</definedName>
-    <definedName name="A2706410A_Latest">Data1!$P$36</definedName>
-    <definedName name="A2706524X">Data1!$H$1:$H$10,Data1!$H$11:$H$36</definedName>
-    <definedName name="A2706524X_Data">Data1!$H$11:$H$36</definedName>
-    <definedName name="A2706524X_Latest">Data1!$H$36</definedName>
-    <definedName name="A2706600R">Data1!$X$1:$X$10,Data1!$X$11:$X$36</definedName>
-    <definedName name="A2706600R_Data">Data1!$X$11:$X$36</definedName>
-    <definedName name="A2706600R_Latest">Data1!$X$36</definedName>
-    <definedName name="A2707474F">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$36</definedName>
-    <definedName name="A2707474F_Data">Data1!$BU$11:$BU$36</definedName>
-    <definedName name="A2707474F_Latest">Data1!$BU$36</definedName>
-    <definedName name="A2707588C">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$36</definedName>
-    <definedName name="A2707588C_Data">Data1!$BW$11:$BW$36</definedName>
-    <definedName name="A2707588C_Latest">Data1!$BW$36</definedName>
-    <definedName name="A2707664V">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$36</definedName>
-    <definedName name="A2707664V_Data">Data1!$BV$11:$BV$36</definedName>
-    <definedName name="A2707664V_Latest">Data1!$BV$36</definedName>
-    <definedName name="A2709868J">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$36</definedName>
-    <definedName name="A2709868J_Data">Data1!$BR$11:$BR$36</definedName>
-    <definedName name="A2709868J_Latest">Data1!$BR$36</definedName>
-    <definedName name="A2709982L">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$36</definedName>
-    <definedName name="A2709982L_Data">Data1!$BT$11:$BT$36</definedName>
-    <definedName name="A2709982L_Latest">Data1!$BT$36</definedName>
-    <definedName name="A2710058C">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$36</definedName>
-    <definedName name="A2710058C_Data">Data1!$BS$11:$BS$36</definedName>
-    <definedName name="A2710058C_Latest">Data1!$BS$36</definedName>
-    <definedName name="A2711578A">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$36</definedName>
-    <definedName name="A2711578A_Data">Data1!$BX$11:$BX$36</definedName>
-    <definedName name="A2711578A_Latest">Data1!$BX$36</definedName>
-    <definedName name="A2711844F">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$36</definedName>
-    <definedName name="A2711844F_Data">Data1!$BZ$11:$BZ$36</definedName>
-    <definedName name="A2711844F_Latest">Data1!$BZ$36</definedName>
-    <definedName name="A2712110L">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$36</definedName>
-    <definedName name="A2712110L_Data">Data1!$CC$11:$CC$36</definedName>
-    <definedName name="A2712110L_Latest">Data1!$CC$36</definedName>
-    <definedName name="A2712226R">Data1!$CW$1:$CW$10,Data1!$CW$11:$CW$36</definedName>
-    <definedName name="A2712226R_Data">Data1!$CW$11:$CW$36</definedName>
-    <definedName name="A2712226R_Latest">Data1!$CW$36</definedName>
-    <definedName name="A2712228V">Data1!$CM$1:$CM$10,Data1!$CM$11:$CM$36</definedName>
-    <definedName name="A2712228V_Data">Data1!$CM$11:$CM$36</definedName>
-    <definedName name="A2712228V_Latest">Data1!$CM$36</definedName>
-    <definedName name="A2712230F">Data1!$CU$1:$CU$10,Data1!$CU$11:$CU$36</definedName>
-    <definedName name="A2712230F_Data">Data1!$CU$11:$CU$36</definedName>
-    <definedName name="A2712230F_Latest">Data1!$CU$36</definedName>
-    <definedName name="A2712232K">Data1!$CP$1:$CP$10,Data1!$CP$11:$CP$36</definedName>
-    <definedName name="A2712232K_Data">Data1!$CP$11:$CP$36</definedName>
-    <definedName name="A2712232K_Latest">Data1!$CP$36</definedName>
-    <definedName name="A2712234R">Data1!$CN$1:$CN$10,Data1!$CN$11:$CN$36</definedName>
-    <definedName name="A2712234R_Data">Data1!$CN$11:$CN$36</definedName>
-    <definedName name="A2712234R_Latest">Data1!$CN$36</definedName>
-    <definedName name="A2712236V">Data1!$CR$1:$CR$10,Data1!$CR$11:$CR$36</definedName>
-    <definedName name="A2712236V_Data">Data1!$CR$11:$CR$36</definedName>
-    <definedName name="A2712236V_Latest">Data1!$CR$36</definedName>
-    <definedName name="A2712238X">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$36</definedName>
-    <definedName name="A2712238X_Data">Data1!$CI$11:$CI$36</definedName>
-    <definedName name="A2712238X_Latest">Data1!$CI$36</definedName>
-    <definedName name="A2712240K">Data1!$CV$1:$CV$10,Data1!$CV$11:$CV$36</definedName>
-    <definedName name="A2712240K_Data">Data1!$CV$11:$CV$36</definedName>
-    <definedName name="A2712240K_Latest">Data1!$CV$36</definedName>
-    <definedName name="A2712242R">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$36</definedName>
-    <definedName name="A2712242R_Data">Data1!$CG$11:$CG$36</definedName>
-    <definedName name="A2712242R_Latest">Data1!$CG$36</definedName>
-    <definedName name="A2712244V">Data1!$CO$1:$CO$10,Data1!$CO$11:$CO$36</definedName>
-    <definedName name="A2712244V_Data">Data1!$CO$11:$CO$36</definedName>
-    <definedName name="A2712244V_Latest">Data1!$CO$36</definedName>
-    <definedName name="A2712246X">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$36</definedName>
-    <definedName name="A2712246X_Data">Data1!$CH$11:$CH$36</definedName>
-    <definedName name="A2712246X_Latest">Data1!$CH$36</definedName>
-    <definedName name="A2712248C">Data1!$CS$1:$CS$10,Data1!$CS$11:$CS$36</definedName>
-    <definedName name="A2712248C_Data">Data1!$CS$11:$CS$36</definedName>
-    <definedName name="A2712248C_Latest">Data1!$CS$36</definedName>
-    <definedName name="A2712250R">Data1!$CT$1:$CT$10,Data1!$CT$11:$CT$36</definedName>
-    <definedName name="A2712250R_Data">Data1!$CT$11:$CT$36</definedName>
-    <definedName name="A2712250R_Latest">Data1!$CT$36</definedName>
-    <definedName name="A2712252V">Data1!$CL$1:$CL$10,Data1!$CL$11:$CL$36</definedName>
-    <definedName name="A2712252V_Data">Data1!$CL$11:$CL$36</definedName>
-    <definedName name="A2712252V_Latest">Data1!$CL$36</definedName>
-    <definedName name="A2712254X">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$36</definedName>
-    <definedName name="A2712254X_Data">Data1!$CK$11:$CK$36</definedName>
-    <definedName name="A2712254X_Latest">Data1!$CK$36</definedName>
-    <definedName name="A2712256C">Data1!$CX$1:$CX$10,Data1!$CX$11:$CX$36</definedName>
-    <definedName name="A2712256C_Data">Data1!$CX$11:$CX$36</definedName>
-    <definedName name="A2712256C_Latest">Data1!$CX$36</definedName>
-    <definedName name="A2712258J">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$36</definedName>
-    <definedName name="A2712258J_Data">Data1!$CJ$11:$CJ$36</definedName>
-    <definedName name="A2712258J_Latest">Data1!$CJ$36</definedName>
-    <definedName name="A2712260V">Data1!$CQ$1:$CQ$10,Data1!$CQ$11:$CQ$36</definedName>
-    <definedName name="A2712260V_Data">Data1!$CQ$11:$CQ$36</definedName>
-    <definedName name="A2712260V_Latest">Data1!$CQ$36</definedName>
-    <definedName name="A2712262X">Data1!$CY$1:$CY$10,Data1!$CY$11:$CY$36</definedName>
-    <definedName name="A2712262X_Data">Data1!$CY$11:$CY$36</definedName>
-    <definedName name="A2712262X_Latest">Data1!$CY$36</definedName>
-    <definedName name="A2712340V">Data1!$DV$1:$DV$10,Data1!$DV$11:$DV$36</definedName>
-    <definedName name="A2712340V_Data">Data1!$DV$11:$DV$36</definedName>
-    <definedName name="A2712340V_Latest">Data1!$DV$36</definedName>
-    <definedName name="A2712342X">Data1!$DL$1:$DL$10,Data1!$DL$11:$DL$36</definedName>
-    <definedName name="A2712342X_Data">Data1!$DL$11:$DL$36</definedName>
-    <definedName name="A2712342X_Latest">Data1!$DL$36</definedName>
-    <definedName name="A2712344C">Data1!$DT$1:$DT$10,Data1!$DT$11:$DT$36</definedName>
-    <definedName name="A2712344C_Data">Data1!$DT$11:$DT$36</definedName>
-    <definedName name="A2712344C_Latest">Data1!$DT$36</definedName>
-    <definedName name="A2712346J">Data1!$DO$1:$DO$10,Data1!$DO$11:$DO$36</definedName>
-    <definedName name="A2712346J_Data">Data1!$DO$11:$DO$36</definedName>
-    <definedName name="A2712346J_Latest">Data1!$DO$36</definedName>
-    <definedName name="A2712348L">Data1!$DM$1:$DM$10,Data1!$DM$11:$DM$36</definedName>
-    <definedName name="A2712348L_Data">Data1!$DM$11:$DM$36</definedName>
-    <definedName name="A2712348L_Latest">Data1!$DM$36</definedName>
-    <definedName name="A2712350X">Data1!$DQ$1:$DQ$10,Data1!$DQ$11:$DQ$36</definedName>
-    <definedName name="A2712350X_Data">Data1!$DQ$11:$DQ$36</definedName>
-    <definedName name="A2712350X_Latest">Data1!$DQ$36</definedName>
-    <definedName name="A2712352C">Data1!$DH$1:$DH$10,Data1!$DH$11:$DH$36</definedName>
-    <definedName name="A2712352C_Data">Data1!$DH$11:$DH$36</definedName>
-    <definedName name="A2712352C_Latest">Data1!$DH$36</definedName>
-    <definedName name="A2712354J">Data1!$DU$1:$DU$10,Data1!$DU$11:$DU$36</definedName>
-    <definedName name="A2712354J_Data">Data1!$DU$11:$DU$36</definedName>
-    <definedName name="A2712354J_Latest">Data1!$DU$36</definedName>
-    <definedName name="A2712356L">Data1!$DF$1:$DF$10,Data1!$DF$11:$DF$36</definedName>
-    <definedName name="A2712356L_Data">Data1!$DF$11:$DF$36</definedName>
-    <definedName name="A2712356L_Latest">Data1!$DF$36</definedName>
-    <definedName name="A2712358T">Data1!$DN$1:$DN$10,Data1!$DN$11:$DN$36</definedName>
-    <definedName name="A2712358T_Data">Data1!$DN$11:$DN$36</definedName>
-    <definedName name="A2712358T_Latest">Data1!$DN$36</definedName>
-    <definedName name="A2712360C">Data1!$DG$1:$DG$10,Data1!$DG$11:$DG$36</definedName>
-    <definedName name="A2712360C_Data">Data1!$DG$11:$DG$36</definedName>
-    <definedName name="A2712360C_Latest">Data1!$DG$36</definedName>
-    <definedName name="A2712362J">Data1!$DR$1:$DR$10,Data1!$DR$11:$DR$36</definedName>
-    <definedName name="A2712362J_Data">Data1!$DR$11:$DR$36</definedName>
-    <definedName name="A2712362J_Latest">Data1!$DR$36</definedName>
-    <definedName name="A2712364L">Data1!$DS$1:$DS$10,Data1!$DS$11:$DS$36</definedName>
-    <definedName name="A2712364L_Data">Data1!$DS$11:$DS$36</definedName>
-    <definedName name="A2712364L_Latest">Data1!$DS$36</definedName>
-    <definedName name="A2712366T">Data1!$DK$1:$DK$10,Data1!$DK$11:$DK$36</definedName>
-    <definedName name="A2712366T_Data">Data1!$DK$11:$DK$36</definedName>
-    <definedName name="A2712366T_Latest">Data1!$DK$36</definedName>
-    <definedName name="A2712368W">Data1!$DJ$1:$DJ$10,Data1!$DJ$11:$DJ$36</definedName>
-    <definedName name="A2712368W_Data">Data1!$DJ$11:$DJ$36</definedName>
-    <definedName name="A2712368W_Latest">Data1!$DJ$36</definedName>
-    <definedName name="A2712370J">Data1!$DW$1:$DW$10,Data1!$DW$11:$DW$36</definedName>
-    <definedName name="A2712370J_Data">Data1!$DW$11:$DW$36</definedName>
-    <definedName name="A2712370J_Latest">Data1!$DW$36</definedName>
-    <definedName name="A2712372L">Data1!$DI$1:$DI$10,Data1!$DI$11:$DI$36</definedName>
-    <definedName name="A2712372L_Data">Data1!$DI$11:$DI$36</definedName>
-    <definedName name="A2712372L_Latest">Data1!$DI$36</definedName>
-    <definedName name="A2712374T">Data1!$DP$1:$DP$10,Data1!$DP$11:$DP$36</definedName>
-    <definedName name="A2712374T_Data">Data1!$DP$11:$DP$36</definedName>
-    <definedName name="A2712374T_Latest">Data1!$DP$36</definedName>
-    <definedName name="A2712376W">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$36</definedName>
-    <definedName name="A2712376W_Data">Data1!$CF$11:$CF$36</definedName>
-    <definedName name="A2712376W_Latest">Data1!$CF$36</definedName>
-    <definedName name="A2712420V">Data1!$DC$1:$DC$10,Data1!$DC$11:$DC$36</definedName>
-    <definedName name="A2712420V_Data">Data1!$DC$11:$DC$36</definedName>
-    <definedName name="A2712420V_Latest">Data1!$DC$36</definedName>
-    <definedName name="A2712426J">Data1!$DA$1:$DA$10,Data1!$DA$11:$DA$36</definedName>
-    <definedName name="A2712426J_Data">Data1!$DA$11:$DA$36</definedName>
-    <definedName name="A2712426J_Latest">Data1!$DA$36</definedName>
-    <definedName name="A2712428L">Data1!$CZ$1:$CZ$10,Data1!$CZ$11:$CZ$36</definedName>
-    <definedName name="A2712428L_Data">Data1!$CZ$11:$CZ$36</definedName>
-    <definedName name="A2712428L_Latest">Data1!$CZ$36</definedName>
-    <definedName name="A2712430X">Data1!$DD$1:$DD$10,Data1!$DD$11:$DD$36</definedName>
-    <definedName name="A2712430X_Data">Data1!$DD$11:$DD$36</definedName>
-    <definedName name="A2712430X_Latest">Data1!$DD$36</definedName>
-    <definedName name="A2712440C">Data1!$DB$1:$DB$10,Data1!$DB$11:$DB$36</definedName>
-    <definedName name="A2712440C_Data">Data1!$DB$11:$DB$36</definedName>
-    <definedName name="A2712440C_Latest">Data1!$DB$36</definedName>
-    <definedName name="A2712452L">Data1!$DE$1:$DE$10,Data1!$DE$11:$DE$36</definedName>
-    <definedName name="A2712452L_Data">Data1!$DE$11:$DE$36</definedName>
-    <definedName name="A2712452L_Latest">Data1!$DE$36</definedName>
-    <definedName name="A2712642A">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$36</definedName>
-    <definedName name="A2712642A_Data">Data1!$CE$11:$CE$36</definedName>
-    <definedName name="A2712642A_Latest">Data1!$CE$36</definedName>
-    <definedName name="A2712908X">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$36</definedName>
-    <definedName name="A2712908X_Data">Data1!$CD$11:$CD$36</definedName>
-    <definedName name="A2712908X_Latest">Data1!$CD$36</definedName>
-    <definedName name="A2713174T">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$36</definedName>
-    <definedName name="A2713174T_Data">Data1!$CB$11:$CB$36</definedName>
-    <definedName name="A2713174T_Latest">Data1!$CB$36</definedName>
-    <definedName name="A2713440W">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$36</definedName>
-    <definedName name="A2713440W_Data">Data1!$BY$11:$BY$36</definedName>
-    <definedName name="A2713440W_Latest">Data1!$BY$36</definedName>
-    <definedName name="A2713706V">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$36</definedName>
-    <definedName name="A2713706V_Data">Data1!$CA$11:$CA$36</definedName>
-    <definedName name="A2713706V_Latest">Data1!$CA$36</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$36</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$36</definedName>
+    <definedName name="A2704282J">Data1!$M$1:$M$10,Data1!$M$11:$M$38</definedName>
+    <definedName name="A2704282J_Data">Data1!$M$11:$M$38</definedName>
+    <definedName name="A2704282J_Latest">Data1!$M$38</definedName>
+    <definedName name="A2704396F">Data1!$E$1:$E$10,Data1!$E$11:$E$38</definedName>
+    <definedName name="A2704396F_Data">Data1!$E$11:$E$38</definedName>
+    <definedName name="A2704396F_Latest">Data1!$E$38</definedName>
+    <definedName name="A2704472W">Data1!$U$1:$U$10,Data1!$U$11:$U$38</definedName>
+    <definedName name="A2704472W_Data">Data1!$U$11:$U$38</definedName>
+    <definedName name="A2704472W_Latest">Data1!$U$38</definedName>
+    <definedName name="A2704548F">Data1!$O$1:$O$10,Data1!$O$11:$O$38</definedName>
+    <definedName name="A2704548F_Data">Data1!$O$11:$O$38</definedName>
+    <definedName name="A2704548F_Latest">Data1!$O$38</definedName>
+    <definedName name="A2704662K">Data1!$G$1:$G$10,Data1!$G$11:$G$38</definedName>
+    <definedName name="A2704662K_Data">Data1!$G$11:$G$38</definedName>
+    <definedName name="A2704662K_Latest">Data1!$G$38</definedName>
+    <definedName name="A2704738V">Data1!$W$1:$W$10,Data1!$W$11:$W$38</definedName>
+    <definedName name="A2704738V_Data">Data1!$W$11:$W$38</definedName>
+    <definedName name="A2704738V_Latest">Data1!$W$38</definedName>
+    <definedName name="A2704814K">Data1!$R$1:$R$10,Data1!$R$11:$R$38</definedName>
+    <definedName name="A2704814K_Data">Data1!$R$11:$R$38</definedName>
+    <definedName name="A2704814K_Latest">Data1!$R$38</definedName>
+    <definedName name="A2704928J">Data1!$J$1:$J$10,Data1!$J$11:$J$38</definedName>
+    <definedName name="A2704928J_Data">Data1!$J$11:$J$38</definedName>
+    <definedName name="A2704928J_Latest">Data1!$J$38</definedName>
+    <definedName name="A2705004A">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$38</definedName>
+    <definedName name="A2705004A_Data">Data1!$Z$11:$Z$38</definedName>
+    <definedName name="A2705004A_Latest">Data1!$Z$38</definedName>
+    <definedName name="A2705044V">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$38</definedName>
+    <definedName name="A2705044V_Data">Data1!$AS$11:$AS$38</definedName>
+    <definedName name="A2705044V_Latest">Data1!$AS$38</definedName>
+    <definedName name="A2705046X">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$38</definedName>
+    <definedName name="A2705046X_Data">Data1!$AI$11:$AI$38</definedName>
+    <definedName name="A2705046X_Latest">Data1!$AI$38</definedName>
+    <definedName name="A2705048C">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$38</definedName>
+    <definedName name="A2705048C_Data">Data1!$AQ$11:$AQ$38</definedName>
+    <definedName name="A2705048C_Latest">Data1!$AQ$38</definedName>
+    <definedName name="A2705050R">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$38</definedName>
+    <definedName name="A2705050R_Data">Data1!$AL$11:$AL$38</definedName>
+    <definedName name="A2705050R_Latest">Data1!$AL$38</definedName>
+    <definedName name="A2705052V">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$38</definedName>
+    <definedName name="A2705052V_Data">Data1!$AJ$11:$AJ$38</definedName>
+    <definedName name="A2705052V_Latest">Data1!$AJ$38</definedName>
+    <definedName name="A2705054X">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$38</definedName>
+    <definedName name="A2705054X_Data">Data1!$AN$11:$AN$38</definedName>
+    <definedName name="A2705054X_Latest">Data1!$AN$38</definedName>
+    <definedName name="A2705056C">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$38</definedName>
+    <definedName name="A2705056C_Data">Data1!$AE$11:$AE$38</definedName>
+    <definedName name="A2705056C_Latest">Data1!$AE$38</definedName>
+    <definedName name="A2705058J">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$38</definedName>
+    <definedName name="A2705058J_Data">Data1!$AR$11:$AR$38</definedName>
+    <definedName name="A2705058J_Latest">Data1!$AR$38</definedName>
+    <definedName name="A2705060V">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$38</definedName>
+    <definedName name="A2705060V_Data">Data1!$AC$11:$AC$38</definedName>
+    <definedName name="A2705060V_Latest">Data1!$AC$38</definedName>
+    <definedName name="A2705062X">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$38</definedName>
+    <definedName name="A2705062X_Data">Data1!$AK$11:$AK$38</definedName>
+    <definedName name="A2705062X_Latest">Data1!$AK$38</definedName>
+    <definedName name="A2705064C">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$38</definedName>
+    <definedName name="A2705064C_Data">Data1!$AD$11:$AD$38</definedName>
+    <definedName name="A2705064C_Latest">Data1!$AD$38</definedName>
+    <definedName name="A2705066J">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$38</definedName>
+    <definedName name="A2705066J_Data">Data1!$AO$11:$AO$38</definedName>
+    <definedName name="A2705066J_Latest">Data1!$AO$38</definedName>
+    <definedName name="A2705068L">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$38</definedName>
+    <definedName name="A2705068L_Data">Data1!$AP$11:$AP$38</definedName>
+    <definedName name="A2705068L_Latest">Data1!$AP$38</definedName>
+    <definedName name="A2705070X">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$38</definedName>
+    <definedName name="A2705070X_Data">Data1!$AH$11:$AH$38</definedName>
+    <definedName name="A2705070X_Latest">Data1!$AH$38</definedName>
+    <definedName name="A2705072C">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$38</definedName>
+    <definedName name="A2705072C_Data">Data1!$AG$11:$AG$38</definedName>
+    <definedName name="A2705072C_Latest">Data1!$AG$38</definedName>
+    <definedName name="A2705074J">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$38</definedName>
+    <definedName name="A2705074J_Data">Data1!$AT$11:$AT$38</definedName>
+    <definedName name="A2705074J_Latest">Data1!$AT$38</definedName>
+    <definedName name="A2705076L">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$38</definedName>
+    <definedName name="A2705076L_Data">Data1!$AF$11:$AF$38</definedName>
+    <definedName name="A2705076L_Latest">Data1!$AF$38</definedName>
+    <definedName name="A2705078T">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$38</definedName>
+    <definedName name="A2705078T_Data">Data1!$AM$11:$AM$38</definedName>
+    <definedName name="A2705078T_Latest">Data1!$AM$38</definedName>
+    <definedName name="A2705080C">Data1!$B$1:$B$10,Data1!$B$11:$B$38</definedName>
+    <definedName name="A2705080C_Data">Data1!$B$11:$B$38</definedName>
+    <definedName name="A2705080C_Latest">Data1!$B$38</definedName>
+    <definedName name="A2705158T">Data1!$BP$1:$BP$10,Data1!$BP$11:$BP$38</definedName>
+    <definedName name="A2705158T_Data">Data1!$BP$11:$BP$38</definedName>
+    <definedName name="A2705158T_Latest">Data1!$BP$38</definedName>
+    <definedName name="A2705160C">Data1!$BF$1:$BF$10,Data1!$BF$11:$BF$38</definedName>
+    <definedName name="A2705160C_Data">Data1!$BF$11:$BF$38</definedName>
+    <definedName name="A2705160C_Latest">Data1!$BF$38</definedName>
+    <definedName name="A2705162J">Data1!$BN$1:$BN$10,Data1!$BN$11:$BN$38</definedName>
+    <definedName name="A2705162J_Data">Data1!$BN$11:$BN$38</definedName>
+    <definedName name="A2705162J_Latest">Data1!$BN$38</definedName>
+    <definedName name="A2705164L">Data1!$BI$1:$BI$10,Data1!$BI$11:$BI$38</definedName>
+    <definedName name="A2705164L_Data">Data1!$BI$11:$BI$38</definedName>
+    <definedName name="A2705164L_Latest">Data1!$BI$38</definedName>
+    <definedName name="A2705166T">Data1!$BG$1:$BG$10,Data1!$BG$11:$BG$38</definedName>
+    <definedName name="A2705166T_Data">Data1!$BG$11:$BG$38</definedName>
+    <definedName name="A2705166T_Latest">Data1!$BG$38</definedName>
+    <definedName name="A2705168W">Data1!$BK$1:$BK$10,Data1!$BK$11:$BK$38</definedName>
+    <definedName name="A2705168W_Data">Data1!$BK$11:$BK$38</definedName>
+    <definedName name="A2705168W_Latest">Data1!$BK$38</definedName>
+    <definedName name="A2705170J">Data1!$BB$1:$BB$10,Data1!$BB$11:$BB$38</definedName>
+    <definedName name="A2705170J_Data">Data1!$BB$11:$BB$38</definedName>
+    <definedName name="A2705170J_Latest">Data1!$BB$38</definedName>
+    <definedName name="A2705172L">Data1!$BO$1:$BO$10,Data1!$BO$11:$BO$38</definedName>
+    <definedName name="A2705172L_Data">Data1!$BO$11:$BO$38</definedName>
+    <definedName name="A2705172L_Latest">Data1!$BO$38</definedName>
+    <definedName name="A2705174T">Data1!$AZ$1:$AZ$10,Data1!$AZ$11:$AZ$38</definedName>
+    <definedName name="A2705174T_Data">Data1!$AZ$11:$AZ$38</definedName>
+    <definedName name="A2705174T_Latest">Data1!$AZ$38</definedName>
+    <definedName name="A2705176W">Data1!$BH$1:$BH$10,Data1!$BH$11:$BH$38</definedName>
+    <definedName name="A2705176W_Data">Data1!$BH$11:$BH$38</definedName>
+    <definedName name="A2705176W_Latest">Data1!$BH$38</definedName>
+    <definedName name="A2705178A">Data1!$BA$1:$BA$10,Data1!$BA$11:$BA$38</definedName>
+    <definedName name="A2705178A_Data">Data1!$BA$11:$BA$38</definedName>
+    <definedName name="A2705178A_Latest">Data1!$BA$38</definedName>
+    <definedName name="A2705180L">Data1!$BL$1:$BL$10,Data1!$BL$11:$BL$38</definedName>
+    <definedName name="A2705180L_Data">Data1!$BL$11:$BL$38</definedName>
+    <definedName name="A2705180L_Latest">Data1!$BL$38</definedName>
+    <definedName name="A2705182T">Data1!$BM$1:$BM$10,Data1!$BM$11:$BM$38</definedName>
+    <definedName name="A2705182T_Data">Data1!$BM$11:$BM$38</definedName>
+    <definedName name="A2705182T_Latest">Data1!$BM$38</definedName>
+    <definedName name="A2705184W">Data1!$BE$1:$BE$10,Data1!$BE$11:$BE$38</definedName>
+    <definedName name="A2705184W_Data">Data1!$BE$11:$BE$38</definedName>
+    <definedName name="A2705184W_Latest">Data1!$BE$38</definedName>
+    <definedName name="A2705186A">Data1!$BD$1:$BD$10,Data1!$BD$11:$BD$38</definedName>
+    <definedName name="A2705186A_Data">Data1!$BD$11:$BD$38</definedName>
+    <definedName name="A2705186A_Latest">Data1!$BD$38</definedName>
+    <definedName name="A2705188F">Data1!$BQ$1:$BQ$10,Data1!$BQ$11:$BQ$38</definedName>
+    <definedName name="A2705188F_Data">Data1!$BQ$11:$BQ$38</definedName>
+    <definedName name="A2705188F_Latest">Data1!$BQ$38</definedName>
+    <definedName name="A2705190T">Data1!$BC$1:$BC$10,Data1!$BC$11:$BC$38</definedName>
+    <definedName name="A2705190T_Data">Data1!$BC$11:$BC$38</definedName>
+    <definedName name="A2705190T_Latest">Data1!$BC$38</definedName>
+    <definedName name="A2705192W">Data1!$BJ$1:$BJ$10,Data1!$BJ$11:$BJ$38</definedName>
+    <definedName name="A2705192W_Data">Data1!$BJ$11:$BJ$38</definedName>
+    <definedName name="A2705192W_Latest">Data1!$BJ$38</definedName>
+    <definedName name="A2705194A">Data1!$D$1:$D$10,Data1!$D$11:$D$38</definedName>
+    <definedName name="A2705194A_Data">Data1!$D$11:$D$38</definedName>
+    <definedName name="A2705194A_Latest">Data1!$D$38</definedName>
+    <definedName name="A2705238T">Data1!$AX$1:$AX$10,Data1!$AX$11:$AX$38</definedName>
+    <definedName name="A2705238T_Data">Data1!$AX$11:$AX$38</definedName>
+    <definedName name="A2705238T_Latest">Data1!$AX$38</definedName>
+    <definedName name="A2705244L">Data1!$AV$1:$AV$10,Data1!$AV$11:$AV$38</definedName>
+    <definedName name="A2705244L_Data">Data1!$AV$11:$AV$38</definedName>
+    <definedName name="A2705244L_Latest">Data1!$AV$38</definedName>
+    <definedName name="A2705246T">Data1!$AU$1:$AU$10,Data1!$AU$11:$AU$38</definedName>
+    <definedName name="A2705246T_Data">Data1!$AU$11:$AU$38</definedName>
+    <definedName name="A2705246T_Latest">Data1!$AU$38</definedName>
+    <definedName name="A2705248W">Data1!$AY$1:$AY$10,Data1!$AY$11:$AY$38</definedName>
+    <definedName name="A2705248W_Data">Data1!$AY$11:$AY$38</definedName>
+    <definedName name="A2705248W_Latest">Data1!$AY$38</definedName>
+    <definedName name="A2705258A">Data1!$AW$1:$AW$10,Data1!$AW$11:$AW$38</definedName>
+    <definedName name="A2705258A_Data">Data1!$AW$11:$AW$38</definedName>
+    <definedName name="A2705258A_Latest">Data1!$AW$38</definedName>
+    <definedName name="A2705270T">Data1!$C$1:$C$10,Data1!$C$11:$C$38</definedName>
+    <definedName name="A2705270T_Data">Data1!$C$11:$C$38</definedName>
+    <definedName name="A2705270T_Latest">Data1!$C$38</definedName>
+    <definedName name="A2705346A">Data1!$T$1:$T$10,Data1!$T$11:$T$38</definedName>
+    <definedName name="A2705346A_Data">Data1!$T$11:$T$38</definedName>
+    <definedName name="A2705346A_Latest">Data1!$T$38</definedName>
+    <definedName name="A2705460F">Data1!$L$1:$L$10,Data1!$L$11:$L$38</definedName>
+    <definedName name="A2705460F_Data">Data1!$L$11:$L$38</definedName>
+    <definedName name="A2705460F_Latest">Data1!$L$38</definedName>
+    <definedName name="A2705536R">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$38</definedName>
+    <definedName name="A2705536R_Data">Data1!$AB$11:$AB$38</definedName>
+    <definedName name="A2705536R_Latest">Data1!$AB$38</definedName>
+    <definedName name="A2705612F">Data1!$S$1:$S$10,Data1!$S$11:$S$38</definedName>
+    <definedName name="A2705612F_Data">Data1!$S$11:$S$38</definedName>
+    <definedName name="A2705612F_Latest">Data1!$S$38</definedName>
+    <definedName name="A2705726C">Data1!$K$1:$K$10,Data1!$K$11:$K$38</definedName>
+    <definedName name="A2705726C_Data">Data1!$K$11:$K$38</definedName>
+    <definedName name="A2705726C_Latest">Data1!$K$38</definedName>
+    <definedName name="A2705802V">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$38</definedName>
+    <definedName name="A2705802V_Data">Data1!$AA$11:$AA$38</definedName>
+    <definedName name="A2705802V_Latest">Data1!$AA$38</definedName>
+    <definedName name="A2705878R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A2705878R_Data">Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A2705878R_Latest">Data1!$Q$38</definedName>
+    <definedName name="A2705992V">Data1!$I$1:$I$10,Data1!$I$11:$I$38</definedName>
+    <definedName name="A2705992V_Data">Data1!$I$11:$I$38</definedName>
+    <definedName name="A2705992V_Latest">Data1!$I$38</definedName>
+    <definedName name="A2706068F">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$38</definedName>
+    <definedName name="A2706068F_Data">Data1!$Y$11:$Y$38</definedName>
+    <definedName name="A2706068F_Latest">Data1!$Y$38</definedName>
+    <definedName name="A2706144W">Data1!$N$1:$N$10,Data1!$N$11:$N$38</definedName>
+    <definedName name="A2706144W_Data">Data1!$N$11:$N$38</definedName>
+    <definedName name="A2706144W_Latest">Data1!$N$38</definedName>
+    <definedName name="A2706258V">Data1!$F$1:$F$10,Data1!$F$11:$F$38</definedName>
+    <definedName name="A2706258V_Data">Data1!$F$11:$F$38</definedName>
+    <definedName name="A2706258V_Latest">Data1!$F$38</definedName>
+    <definedName name="A2706334K">Data1!$V$1:$V$10,Data1!$V$11:$V$38</definedName>
+    <definedName name="A2706334K_Data">Data1!$V$11:$V$38</definedName>
+    <definedName name="A2706334K_Latest">Data1!$V$38</definedName>
+    <definedName name="A2706410A">Data1!$P$1:$P$10,Data1!$P$11:$P$38</definedName>
+    <definedName name="A2706410A_Data">Data1!$P$11:$P$38</definedName>
+    <definedName name="A2706410A_Latest">Data1!$P$38</definedName>
+    <definedName name="A2706524X">Data1!$H$1:$H$10,Data1!$H$11:$H$38</definedName>
+    <definedName name="A2706524X_Data">Data1!$H$11:$H$38</definedName>
+    <definedName name="A2706524X_Latest">Data1!$H$38</definedName>
+    <definedName name="A2706600R">Data1!$X$1:$X$10,Data1!$X$11:$X$38</definedName>
+    <definedName name="A2706600R_Data">Data1!$X$11:$X$38</definedName>
+    <definedName name="A2706600R_Latest">Data1!$X$38</definedName>
+    <definedName name="A2707474F">Data1!$BU$1:$BU$10,Data1!$BU$11:$BU$38</definedName>
+    <definedName name="A2707474F_Data">Data1!$BU$11:$BU$38</definedName>
+    <definedName name="A2707474F_Latest">Data1!$BU$38</definedName>
+    <definedName name="A2707588C">Data1!$BW$1:$BW$10,Data1!$BW$11:$BW$38</definedName>
+    <definedName name="A2707588C_Data">Data1!$BW$11:$BW$38</definedName>
+    <definedName name="A2707588C_Latest">Data1!$BW$38</definedName>
+    <definedName name="A2707664V">Data1!$BV$1:$BV$10,Data1!$BV$11:$BV$38</definedName>
+    <definedName name="A2707664V_Data">Data1!$BV$11:$BV$38</definedName>
+    <definedName name="A2707664V_Latest">Data1!$BV$38</definedName>
+    <definedName name="A2709868J">Data1!$BR$1:$BR$10,Data1!$BR$11:$BR$38</definedName>
+    <definedName name="A2709868J_Data">Data1!$BR$11:$BR$38</definedName>
+    <definedName name="A2709868J_Latest">Data1!$BR$38</definedName>
+    <definedName name="A2709982L">Data1!$BT$1:$BT$10,Data1!$BT$11:$BT$38</definedName>
+    <definedName name="A2709982L_Data">Data1!$BT$11:$BT$38</definedName>
+    <definedName name="A2709982L_Latest">Data1!$BT$38</definedName>
+    <definedName name="A2710058C">Data1!$BS$1:$BS$10,Data1!$BS$11:$BS$38</definedName>
+    <definedName name="A2710058C_Data">Data1!$BS$11:$BS$38</definedName>
+    <definedName name="A2710058C_Latest">Data1!$BS$38</definedName>
+    <definedName name="A2711578A">Data1!$BX$1:$BX$10,Data1!$BX$11:$BX$38</definedName>
+    <definedName name="A2711578A_Data">Data1!$BX$11:$BX$38</definedName>
+    <definedName name="A2711578A_Latest">Data1!$BX$38</definedName>
+    <definedName name="A2711844F">Data1!$BZ$1:$BZ$10,Data1!$BZ$11:$BZ$38</definedName>
+    <definedName name="A2711844F_Data">Data1!$BZ$11:$BZ$38</definedName>
+    <definedName name="A2711844F_Latest">Data1!$BZ$38</definedName>
+    <definedName name="A2712110L">Data1!$CC$1:$CC$10,Data1!$CC$11:$CC$38</definedName>
+    <definedName name="A2712110L_Data">Data1!$CC$11:$CC$38</definedName>
+    <definedName name="A2712110L_Latest">Data1!$CC$38</definedName>
+    <definedName name="A2712226R">Data1!$CW$1:$CW$10,Data1!$CW$11:$CW$38</definedName>
+    <definedName name="A2712226R_Data">Data1!$CW$11:$CW$38</definedName>
+    <definedName name="A2712226R_Latest">Data1!$CW$38</definedName>
+    <definedName name="A2712228V">Data1!$CM$1:$CM$10,Data1!$CM$11:$CM$38</definedName>
+    <definedName name="A2712228V_Data">Data1!$CM$11:$CM$38</definedName>
+    <definedName name="A2712228V_Latest">Data1!$CM$38</definedName>
+    <definedName name="A2712230F">Data1!$CU$1:$CU$10,Data1!$CU$11:$CU$38</definedName>
+    <definedName name="A2712230F_Data">Data1!$CU$11:$CU$38</definedName>
+    <definedName name="A2712230F_Latest">Data1!$CU$38</definedName>
+    <definedName name="A2712232K">Data1!$CP$1:$CP$10,Data1!$CP$11:$CP$38</definedName>
+    <definedName name="A2712232K_Data">Data1!$CP$11:$CP$38</definedName>
+    <definedName name="A2712232K_Latest">Data1!$CP$38</definedName>
+    <definedName name="A2712234R">Data1!$CN$1:$CN$10,Data1!$CN$11:$CN$38</definedName>
+    <definedName name="A2712234R_Data">Data1!$CN$11:$CN$38</definedName>
+    <definedName name="A2712234R_Latest">Data1!$CN$38</definedName>
+    <definedName name="A2712236V">Data1!$CR$1:$CR$10,Data1!$CR$11:$CR$38</definedName>
+    <definedName name="A2712236V_Data">Data1!$CR$11:$CR$38</definedName>
+    <definedName name="A2712236V_Latest">Data1!$CR$38</definedName>
+    <definedName name="A2712238X">Data1!$CI$1:$CI$10,Data1!$CI$11:$CI$38</definedName>
+    <definedName name="A2712238X_Data">Data1!$CI$11:$CI$38</definedName>
+    <definedName name="A2712238X_Latest">Data1!$CI$38</definedName>
+    <definedName name="A2712240K">Data1!$CV$1:$CV$10,Data1!$CV$11:$CV$38</definedName>
+    <definedName name="A2712240K_Data">Data1!$CV$11:$CV$38</definedName>
+    <definedName name="A2712240K_Latest">Data1!$CV$38</definedName>
+    <definedName name="A2712242R">Data1!$CG$1:$CG$10,Data1!$CG$11:$CG$38</definedName>
+    <definedName name="A2712242R_Data">Data1!$CG$11:$CG$38</definedName>
+    <definedName name="A2712242R_Latest">Data1!$CG$38</definedName>
+    <definedName name="A2712244V">Data1!$CO$1:$CO$10,Data1!$CO$11:$CO$38</definedName>
+    <definedName name="A2712244V_Data">Data1!$CO$11:$CO$38</definedName>
+    <definedName name="A2712244V_Latest">Data1!$CO$38</definedName>
+    <definedName name="A2712246X">Data1!$CH$1:$CH$10,Data1!$CH$11:$CH$38</definedName>
+    <definedName name="A2712246X_Data">Data1!$CH$11:$CH$38</definedName>
+    <definedName name="A2712246X_Latest">Data1!$CH$38</definedName>
+    <definedName name="A2712248C">Data1!$CS$1:$CS$10,Data1!$CS$11:$CS$38</definedName>
+    <definedName name="A2712248C_Data">Data1!$CS$11:$CS$38</definedName>
+    <definedName name="A2712248C_Latest">Data1!$CS$38</definedName>
+    <definedName name="A2712250R">Data1!$CT$1:$CT$10,Data1!$CT$11:$CT$38</definedName>
+    <definedName name="A2712250R_Data">Data1!$CT$11:$CT$38</definedName>
+    <definedName name="A2712250R_Latest">Data1!$CT$38</definedName>
+    <definedName name="A2712252V">Data1!$CL$1:$CL$10,Data1!$CL$11:$CL$38</definedName>
+    <definedName name="A2712252V_Data">Data1!$CL$11:$CL$38</definedName>
+    <definedName name="A2712252V_Latest">Data1!$CL$38</definedName>
+    <definedName name="A2712254X">Data1!$CK$1:$CK$10,Data1!$CK$11:$CK$38</definedName>
+    <definedName name="A2712254X_Data">Data1!$CK$11:$CK$38</definedName>
+    <definedName name="A2712254X_Latest">Data1!$CK$38</definedName>
+    <definedName name="A2712256C">Data1!$CX$1:$CX$10,Data1!$CX$11:$CX$38</definedName>
+    <definedName name="A2712256C_Data">Data1!$CX$11:$CX$38</definedName>
+    <definedName name="A2712256C_Latest">Data1!$CX$38</definedName>
+    <definedName name="A2712258J">Data1!$CJ$1:$CJ$10,Data1!$CJ$11:$CJ$38</definedName>
+    <definedName name="A2712258J_Data">Data1!$CJ$11:$CJ$38</definedName>
+    <definedName name="A2712258J_Latest">Data1!$CJ$38</definedName>
+    <definedName name="A2712260V">Data1!$CQ$1:$CQ$10,Data1!$CQ$11:$CQ$38</definedName>
+    <definedName name="A2712260V_Data">Data1!$CQ$11:$CQ$38</definedName>
+    <definedName name="A2712260V_Latest">Data1!$CQ$38</definedName>
+    <definedName name="A2712262X">Data1!$CY$1:$CY$10,Data1!$CY$11:$CY$38</definedName>
+    <definedName name="A2712262X_Data">Data1!$CY$11:$CY$38</definedName>
+    <definedName name="A2712262X_Latest">Data1!$CY$38</definedName>
+    <definedName name="A2712340V">Data1!$DV$1:$DV$10,Data1!$DV$11:$DV$38</definedName>
+    <definedName name="A2712340V_Data">Data1!$DV$11:$DV$38</definedName>
+    <definedName name="A2712340V_Latest">Data1!$DV$38</definedName>
+    <definedName name="A2712342X">Data1!$DL$1:$DL$10,Data1!$DL$11:$DL$38</definedName>
+    <definedName name="A2712342X_Data">Data1!$DL$11:$DL$38</definedName>
+    <definedName name="A2712342X_Latest">Data1!$DL$38</definedName>
+    <definedName name="A2712344C">Data1!$DT$1:$DT$10,Data1!$DT$11:$DT$38</definedName>
+    <definedName name="A2712344C_Data">Data1!$DT$11:$DT$38</definedName>
+    <definedName name="A2712344C_Latest">Data1!$DT$38</definedName>
+    <definedName name="A2712346J">Data1!$DO$1:$DO$10,Data1!$DO$11:$DO$38</definedName>
+    <definedName name="A2712346J_Data">Data1!$DO$11:$DO$38</definedName>
+    <definedName name="A2712346J_Latest">Data1!$DO$38</definedName>
+    <definedName name="A2712348L">Data1!$DM$1:$DM$10,Data1!$DM$11:$DM$38</definedName>
+    <definedName name="A2712348L_Data">Data1!$DM$11:$DM$38</definedName>
+    <definedName name="A2712348L_Latest">Data1!$DM$38</definedName>
+    <definedName name="A2712350X">Data1!$DQ$1:$DQ$10,Data1!$DQ$11:$DQ$38</definedName>
+    <definedName name="A2712350X_Data">Data1!$DQ$11:$DQ$38</definedName>
+    <definedName name="A2712350X_Latest">Data1!$DQ$38</definedName>
+    <definedName name="A2712352C">Data1!$DH$1:$DH$10,Data1!$DH$11:$DH$38</definedName>
+    <definedName name="A2712352C_Data">Data1!$DH$11:$DH$38</definedName>
+    <definedName name="A2712352C_Latest">Data1!$DH$38</definedName>
+    <definedName name="A2712354J">Data1!$DU$1:$DU$10,Data1!$DU$11:$DU$38</definedName>
+    <definedName name="A2712354J_Data">Data1!$DU$11:$DU$38</definedName>
+    <definedName name="A2712354J_Latest">Data1!$DU$38</definedName>
+    <definedName name="A2712356L">Data1!$DF$1:$DF$10,Data1!$DF$11:$DF$38</definedName>
+    <definedName name="A2712356L_Data">Data1!$DF$11:$DF$38</definedName>
+    <definedName name="A2712356L_Latest">Data1!$DF$38</definedName>
+    <definedName name="A2712358T">Data1!$DN$1:$DN$10,Data1!$DN$11:$DN$38</definedName>
+    <definedName name="A2712358T_Data">Data1!$DN$11:$DN$38</definedName>
+    <definedName name="A2712358T_Latest">Data1!$DN$38</definedName>
+    <definedName name="A2712360C">Data1!$DG$1:$DG$10,Data1!$DG$11:$DG$38</definedName>
+    <definedName name="A2712360C_Data">Data1!$DG$11:$DG$38</definedName>
+    <definedName name="A2712360C_Latest">Data1!$DG$38</definedName>
+    <definedName name="A2712362J">Data1!$DR$1:$DR$10,Data1!$DR$11:$DR$38</definedName>
+    <definedName name="A2712362J_Data">Data1!$DR$11:$DR$38</definedName>
+    <definedName name="A2712362J_Latest">Data1!$DR$38</definedName>
+    <definedName name="A2712364L">Data1!$DS$1:$DS$10,Data1!$DS$11:$DS$38</definedName>
+    <definedName name="A2712364L_Data">Data1!$DS$11:$DS$38</definedName>
+    <definedName name="A2712364L_Latest">Data1!$DS$38</definedName>
+    <definedName name="A2712366T">Data1!$DK$1:$DK$10,Data1!$DK$11:$DK$38</definedName>
+    <definedName name="A2712366T_Data">Data1!$DK$11:$DK$38</definedName>
+    <definedName name="A2712366T_Latest">Data1!$DK$38</definedName>
+    <definedName name="A2712368W">Data1!$DJ$1:$DJ$10,Data1!$DJ$11:$DJ$38</definedName>
+    <definedName name="A2712368W_Data">Data1!$DJ$11:$DJ$38</definedName>
+    <definedName name="A2712368W_Latest">Data1!$DJ$38</definedName>
+    <definedName name="A2712370J">Data1!$DW$1:$DW$10,Data1!$DW$11:$DW$38</definedName>
+    <definedName name="A2712370J_Data">Data1!$DW$11:$DW$38</definedName>
+    <definedName name="A2712370J_Latest">Data1!$DW$38</definedName>
+    <definedName name="A2712372L">Data1!$DI$1:$DI$10,Data1!$DI$11:$DI$38</definedName>
+    <definedName name="A2712372L_Data">Data1!$DI$11:$DI$38</definedName>
+    <definedName name="A2712372L_Latest">Data1!$DI$38</definedName>
+    <definedName name="A2712374T">Data1!$DP$1:$DP$10,Data1!$DP$11:$DP$38</definedName>
+    <definedName name="A2712374T_Data">Data1!$DP$11:$DP$38</definedName>
+    <definedName name="A2712374T_Latest">Data1!$DP$38</definedName>
+    <definedName name="A2712376W">Data1!$CF$1:$CF$10,Data1!$CF$11:$CF$38</definedName>
+    <definedName name="A2712376W_Data">Data1!$CF$11:$CF$38</definedName>
+    <definedName name="A2712376W_Latest">Data1!$CF$38</definedName>
+    <definedName name="A2712420V">Data1!$DC$1:$DC$10,Data1!$DC$11:$DC$38</definedName>
+    <definedName name="A2712420V_Data">Data1!$DC$11:$DC$38</definedName>
+    <definedName name="A2712420V_Latest">Data1!$DC$38</definedName>
+    <definedName name="A2712426J">Data1!$DA$1:$DA$10,Data1!$DA$11:$DA$38</definedName>
+    <definedName name="A2712426J_Data">Data1!$DA$11:$DA$38</definedName>
+    <definedName name="A2712426J_Latest">Data1!$DA$38</definedName>
+    <definedName name="A2712428L">Data1!$CZ$1:$CZ$10,Data1!$CZ$11:$CZ$38</definedName>
+    <definedName name="A2712428L_Data">Data1!$CZ$11:$CZ$38</definedName>
+    <definedName name="A2712428L_Latest">Data1!$CZ$38</definedName>
+    <definedName name="A2712430X">Data1!$DD$1:$DD$10,Data1!$DD$11:$DD$38</definedName>
+    <definedName name="A2712430X_Data">Data1!$DD$11:$DD$38</definedName>
+    <definedName name="A2712430X_Latest">Data1!$DD$38</definedName>
+    <definedName name="A2712440C">Data1!$DB$1:$DB$10,Data1!$DB$11:$DB$38</definedName>
+    <definedName name="A2712440C_Data">Data1!$DB$11:$DB$38</definedName>
+    <definedName name="A2712440C_Latest">Data1!$DB$38</definedName>
+    <definedName name="A2712452L">Data1!$DE$1:$DE$10,Data1!$DE$11:$DE$38</definedName>
+    <definedName name="A2712452L_Data">Data1!$DE$11:$DE$38</definedName>
+    <definedName name="A2712452L_Latest">Data1!$DE$38</definedName>
+    <definedName name="A2712642A">Data1!$CE$1:$CE$10,Data1!$CE$11:$CE$38</definedName>
+    <definedName name="A2712642A_Data">Data1!$CE$11:$CE$38</definedName>
+    <definedName name="A2712642A_Latest">Data1!$CE$38</definedName>
+    <definedName name="A2712908X">Data1!$CD$1:$CD$10,Data1!$CD$11:$CD$38</definedName>
+    <definedName name="A2712908X_Data">Data1!$CD$11:$CD$38</definedName>
+    <definedName name="A2712908X_Latest">Data1!$CD$38</definedName>
+    <definedName name="A2713174T">Data1!$CB$1:$CB$10,Data1!$CB$11:$CB$38</definedName>
+    <definedName name="A2713174T_Data">Data1!$CB$11:$CB$38</definedName>
+    <definedName name="A2713174T_Latest">Data1!$CB$38</definedName>
+    <definedName name="A2713440W">Data1!$BY$1:$BY$10,Data1!$BY$11:$BY$38</definedName>
+    <definedName name="A2713440W_Data">Data1!$BY$11:$BY$38</definedName>
+    <definedName name="A2713440W_Latest">Data1!$BY$38</definedName>
+    <definedName name="A2713706V">Data1!$CA$1:$CA$10,Data1!$CA$11:$CA$38</definedName>
+    <definedName name="A2713706V_Data">Data1!$CA$11:$CA$38</definedName>
+    <definedName name="A2713706V_Latest">Data1!$CA$38</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$38</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -4808,7 +4808,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -5489,10 +5489,10 @@
         <v>35947</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H12" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>135</v>
@@ -5521,10 +5521,10 @@
         <v>35947</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H13" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>135</v>
@@ -5553,10 +5553,10 @@
         <v>35947</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H14" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>135</v>
@@ -5585,10 +5585,10 @@
         <v>35947</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H15" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>135</v>
@@ -5617,10 +5617,10 @@
         <v>35947</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H16" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>135</v>
@@ -5649,10 +5649,10 @@
         <v>35947</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H17" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>135</v>
@@ -5681,10 +5681,10 @@
         <v>35947</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H18" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>135</v>
@@ -5713,10 +5713,10 @@
         <v>35947</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H19" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>135</v>
@@ -5745,10 +5745,10 @@
         <v>35947</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H20" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>135</v>
@@ -5777,10 +5777,10 @@
         <v>35947</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H21" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>135</v>
@@ -5809,10 +5809,10 @@
         <v>35947</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H22" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>135</v>
@@ -5841,10 +5841,10 @@
         <v>35947</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H23" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>135</v>
@@ -5873,10 +5873,10 @@
         <v>35947</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H24" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>135</v>
@@ -5905,10 +5905,10 @@
         <v>35947</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H25" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>135</v>
@@ -5937,10 +5937,10 @@
         <v>35947</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H26" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>135</v>
@@ -5969,10 +5969,10 @@
         <v>35947</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H27" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>135</v>
@@ -6001,10 +6001,10 @@
         <v>35947</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H28" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>135</v>
@@ -6033,10 +6033,10 @@
         <v>35947</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H29" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>135</v>
@@ -6065,10 +6065,10 @@
         <v>35947</v>
       </c>
       <c r="G30" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H30" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>135</v>
@@ -6097,10 +6097,10 @@
         <v>35947</v>
       </c>
       <c r="G31" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H31" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>135</v>
@@ -6129,10 +6129,10 @@
         <v>35947</v>
       </c>
       <c r="G32" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H32" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>135</v>
@@ -6161,10 +6161,10 @@
         <v>35947</v>
       </c>
       <c r="G33" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H33" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>135</v>
@@ -6193,10 +6193,10 @@
         <v>35947</v>
       </c>
       <c r="G34" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H34" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>135</v>
@@ -6225,10 +6225,10 @@
         <v>35947</v>
       </c>
       <c r="G35" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H35" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>135</v>
@@ -6257,10 +6257,10 @@
         <v>35947</v>
       </c>
       <c r="G36" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H36" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>135</v>
@@ -6289,10 +6289,10 @@
         <v>35947</v>
       </c>
       <c r="G37" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H37" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>135</v>
@@ -6321,10 +6321,10 @@
         <v>35947</v>
       </c>
       <c r="G38" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H38" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>135</v>
@@ -6353,10 +6353,10 @@
         <v>35947</v>
       </c>
       <c r="G39" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H39" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>135</v>
@@ -6385,10 +6385,10 @@
         <v>35947</v>
       </c>
       <c r="G40" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H40" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>135</v>
@@ -6417,10 +6417,10 @@
         <v>35947</v>
       </c>
       <c r="G41" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H41" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>135</v>
@@ -6449,10 +6449,10 @@
         <v>35947</v>
       </c>
       <c r="G42" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H42" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>135</v>
@@ -6481,10 +6481,10 @@
         <v>35947</v>
       </c>
       <c r="G43" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H43" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>135</v>
@@ -6513,10 +6513,10 @@
         <v>35947</v>
       </c>
       <c r="G44" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H44" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>135</v>
@@ -6545,10 +6545,10 @@
         <v>35947</v>
       </c>
       <c r="G45" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H45" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>135</v>
@@ -6577,10 +6577,10 @@
         <v>35947</v>
       </c>
       <c r="G46" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H46" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>135</v>
@@ -6609,10 +6609,10 @@
         <v>35947</v>
       </c>
       <c r="G47" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H47" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>135</v>
@@ -6641,10 +6641,10 @@
         <v>35947</v>
       </c>
       <c r="G48" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H48" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>135</v>
@@ -6673,10 +6673,10 @@
         <v>35947</v>
       </c>
       <c r="G49" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H49" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>135</v>
@@ -6705,10 +6705,10 @@
         <v>35947</v>
       </c>
       <c r="G50" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H50" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I50" s="10" t="s">
         <v>135</v>
@@ -6737,10 +6737,10 @@
         <v>35947</v>
       </c>
       <c r="G51" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H51" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I51" s="10" t="s">
         <v>135</v>
@@ -6769,10 +6769,10 @@
         <v>35947</v>
       </c>
       <c r="G52" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H52" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>135</v>
@@ -6801,10 +6801,10 @@
         <v>35947</v>
       </c>
       <c r="G53" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H53" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>135</v>
@@ -6833,10 +6833,10 @@
         <v>35947</v>
       </c>
       <c r="G54" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H54" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>135</v>
@@ -6865,10 +6865,10 @@
         <v>35947</v>
       </c>
       <c r="G55" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H55" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I55" s="10" t="s">
         <v>135</v>
@@ -6897,10 +6897,10 @@
         <v>35947</v>
       </c>
       <c r="G56" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H56" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" s="10" t="s">
         <v>135</v>
@@ -6929,10 +6929,10 @@
         <v>35947</v>
       </c>
       <c r="G57" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H57" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I57" s="10" t="s">
         <v>135</v>
@@ -6961,10 +6961,10 @@
         <v>35947</v>
       </c>
       <c r="G58" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H58" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I58" s="10" t="s">
         <v>135</v>
@@ -6993,10 +6993,10 @@
         <v>35947</v>
       </c>
       <c r="G59" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H59" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I59" s="10" t="s">
         <v>135</v>
@@ -7025,10 +7025,10 @@
         <v>35947</v>
       </c>
       <c r="G60" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H60" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I60" s="10" t="s">
         <v>135</v>
@@ -7057,10 +7057,10 @@
         <v>35947</v>
       </c>
       <c r="G61" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H61" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>135</v>
@@ -7089,10 +7089,10 @@
         <v>35947</v>
       </c>
       <c r="G62" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H62" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>135</v>
@@ -7121,10 +7121,10 @@
         <v>35947</v>
       </c>
       <c r="G63" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H63" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I63" s="10" t="s">
         <v>135</v>
@@ -7153,10 +7153,10 @@
         <v>35947</v>
       </c>
       <c r="G64" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H64" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I64" s="10" t="s">
         <v>135</v>
@@ -7185,10 +7185,10 @@
         <v>35947</v>
       </c>
       <c r="G65" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H65" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>135</v>
@@ -7217,10 +7217,10 @@
         <v>35947</v>
       </c>
       <c r="G66" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H66" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>135</v>
@@ -7249,10 +7249,10 @@
         <v>35947</v>
       </c>
       <c r="G67" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H67" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>135</v>
@@ -7281,10 +7281,10 @@
         <v>35947</v>
       </c>
       <c r="G68" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H68" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>135</v>
@@ -7313,10 +7313,10 @@
         <v>35947</v>
       </c>
       <c r="G69" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H69" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I69" s="10" t="s">
         <v>135</v>
@@ -7345,10 +7345,10 @@
         <v>35947</v>
       </c>
       <c r="G70" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H70" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I70" s="10" t="s">
         <v>135</v>
@@ -7377,10 +7377,10 @@
         <v>35947</v>
       </c>
       <c r="G71" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H71" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>135</v>
@@ -7409,10 +7409,10 @@
         <v>35947</v>
       </c>
       <c r="G72" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H72" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>135</v>
@@ -7441,10 +7441,10 @@
         <v>35947</v>
       </c>
       <c r="G73" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H73" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>135</v>
@@ -7473,10 +7473,10 @@
         <v>35947</v>
       </c>
       <c r="G74" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H74" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>135</v>
@@ -7505,10 +7505,10 @@
         <v>35947</v>
       </c>
       <c r="G75" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H75" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I75" s="10" t="s">
         <v>135</v>
@@ -7537,10 +7537,10 @@
         <v>35947</v>
       </c>
       <c r="G76" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H76" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I76" s="10" t="s">
         <v>135</v>
@@ -7569,10 +7569,10 @@
         <v>35947</v>
       </c>
       <c r="G77" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H77" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>135</v>
@@ -7601,10 +7601,10 @@
         <v>35947</v>
       </c>
       <c r="G78" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H78" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>135</v>
@@ -7633,10 +7633,10 @@
         <v>35947</v>
       </c>
       <c r="G79" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H79" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>135</v>
@@ -7665,10 +7665,10 @@
         <v>35947</v>
       </c>
       <c r="G80" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H80" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>135</v>
@@ -7697,10 +7697,10 @@
         <v>35947</v>
       </c>
       <c r="G81" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H81" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I81" s="10" t="s">
         <v>135</v>
@@ -7729,10 +7729,10 @@
         <v>35947</v>
       </c>
       <c r="G82" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H82" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I82" s="10" t="s">
         <v>135</v>
@@ -7761,10 +7761,10 @@
         <v>35947</v>
       </c>
       <c r="G83" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H83" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>135</v>
@@ -7793,10 +7793,10 @@
         <v>35947</v>
       </c>
       <c r="G84" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H84" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>135</v>
@@ -7825,10 +7825,10 @@
         <v>35947</v>
       </c>
       <c r="G85" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H85" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>135</v>
@@ -7857,10 +7857,10 @@
         <v>35947</v>
       </c>
       <c r="G86" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H86" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>135</v>
@@ -7889,10 +7889,10 @@
         <v>35947</v>
       </c>
       <c r="G87" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H87" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I87" s="10" t="s">
         <v>135</v>
@@ -7921,10 +7921,10 @@
         <v>35947</v>
       </c>
       <c r="G88" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H88" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I88" s="10" t="s">
         <v>135</v>
@@ -7953,10 +7953,10 @@
         <v>35947</v>
       </c>
       <c r="G89" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H89" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I89" s="10" t="s">
         <v>135</v>
@@ -7985,10 +7985,10 @@
         <v>35947</v>
       </c>
       <c r="G90" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H90" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I90" s="10" t="s">
         <v>135</v>
@@ -8017,10 +8017,10 @@
         <v>35947</v>
       </c>
       <c r="G91" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H91" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>135</v>
@@ -8049,10 +8049,10 @@
         <v>35947</v>
       </c>
       <c r="G92" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H92" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I92" s="10" t="s">
         <v>135</v>
@@ -8081,10 +8081,10 @@
         <v>35947</v>
       </c>
       <c r="G93" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H93" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I93" s="10" t="s">
         <v>135</v>
@@ -8113,10 +8113,10 @@
         <v>35947</v>
       </c>
       <c r="G94" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H94" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I94" s="10" t="s">
         <v>135</v>
@@ -8145,10 +8145,10 @@
         <v>35947</v>
       </c>
       <c r="G95" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H95" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I95" s="10" t="s">
         <v>135</v>
@@ -8177,10 +8177,10 @@
         <v>35947</v>
       </c>
       <c r="G96" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H96" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I96" s="10" t="s">
         <v>135</v>
@@ -8209,10 +8209,10 @@
         <v>35947</v>
       </c>
       <c r="G97" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H97" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I97" s="10" t="s">
         <v>135</v>
@@ -8241,10 +8241,10 @@
         <v>35947</v>
       </c>
       <c r="G98" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H98" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I98" s="10" t="s">
         <v>135</v>
@@ -8273,10 +8273,10 @@
         <v>35947</v>
       </c>
       <c r="G99" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H99" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>135</v>
@@ -8305,10 +8305,10 @@
         <v>35947</v>
       </c>
       <c r="G100" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H100" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>135</v>
@@ -8337,10 +8337,10 @@
         <v>35947</v>
       </c>
       <c r="G101" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H101" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I101" s="10" t="s">
         <v>135</v>
@@ -8369,10 +8369,10 @@
         <v>35947</v>
       </c>
       <c r="G102" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H102" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I102" s="10" t="s">
         <v>135</v>
@@ -8401,10 +8401,10 @@
         <v>35947</v>
       </c>
       <c r="G103" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H103" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I103" s="10" t="s">
         <v>135</v>
@@ -8433,10 +8433,10 @@
         <v>35947</v>
       </c>
       <c r="G104" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H104" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I104" s="10" t="s">
         <v>135</v>
@@ -8465,10 +8465,10 @@
         <v>35947</v>
       </c>
       <c r="G105" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H105" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I105" s="10" t="s">
         <v>135</v>
@@ -8497,10 +8497,10 @@
         <v>35947</v>
       </c>
       <c r="G106" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H106" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>135</v>
@@ -8529,10 +8529,10 @@
         <v>35947</v>
       </c>
       <c r="G107" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H107" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I107" s="10" t="s">
         <v>135</v>
@@ -8561,10 +8561,10 @@
         <v>35947</v>
       </c>
       <c r="G108" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H108" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I108" s="10" t="s">
         <v>135</v>
@@ -8593,10 +8593,10 @@
         <v>35947</v>
       </c>
       <c r="G109" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H109" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I109" s="10" t="s">
         <v>135</v>
@@ -8625,10 +8625,10 @@
         <v>35947</v>
       </c>
       <c r="G110" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H110" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I110" s="10" t="s">
         <v>135</v>
@@ -8657,10 +8657,10 @@
         <v>35947</v>
       </c>
       <c r="G111" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H111" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I111" s="10" t="s">
         <v>135</v>
@@ -8689,10 +8689,10 @@
         <v>35947</v>
       </c>
       <c r="G112" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H112" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I112" s="10" t="s">
         <v>135</v>
@@ -8721,10 +8721,10 @@
         <v>35947</v>
       </c>
       <c r="G113" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H113" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I113" s="10" t="s">
         <v>135</v>
@@ -8753,10 +8753,10 @@
         <v>35947</v>
       </c>
       <c r="G114" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H114" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>135</v>
@@ -8785,10 +8785,10 @@
         <v>35947</v>
       </c>
       <c r="G115" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H115" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I115" s="10" t="s">
         <v>135</v>
@@ -8817,10 +8817,10 @@
         <v>35947</v>
       </c>
       <c r="G116" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H116" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I116" s="10" t="s">
         <v>135</v>
@@ -8849,10 +8849,10 @@
         <v>35947</v>
       </c>
       <c r="G117" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H117" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I117" s="10" t="s">
         <v>135</v>
@@ -8881,10 +8881,10 @@
         <v>35947</v>
       </c>
       <c r="G118" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H118" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I118" s="10" t="s">
         <v>135</v>
@@ -8913,10 +8913,10 @@
         <v>35947</v>
       </c>
       <c r="G119" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H119" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I119" s="10" t="s">
         <v>135</v>
@@ -8945,10 +8945,10 @@
         <v>35947</v>
       </c>
       <c r="G120" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H120" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
         <v>135</v>
@@ -8977,10 +8977,10 @@
         <v>35947</v>
       </c>
       <c r="G121" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H121" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I121" s="10" t="s">
         <v>135</v>
@@ -9009,10 +9009,10 @@
         <v>35947</v>
       </c>
       <c r="G122" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H122" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I122" s="10" t="s">
         <v>135</v>
@@ -9041,10 +9041,10 @@
         <v>35947</v>
       </c>
       <c r="G123" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H123" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I123" s="10" t="s">
         <v>135</v>
@@ -9073,10 +9073,10 @@
         <v>35947</v>
       </c>
       <c r="G124" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H124" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I124" s="10" t="s">
         <v>135</v>
@@ -9105,10 +9105,10 @@
         <v>35947</v>
       </c>
       <c r="G125" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H125" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I125" s="10" t="s">
         <v>135</v>
@@ -9137,10 +9137,10 @@
         <v>35947</v>
       </c>
       <c r="G126" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H126" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I126" s="10" t="s">
         <v>135</v>
@@ -9169,10 +9169,10 @@
         <v>35947</v>
       </c>
       <c r="G127" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H127" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I127" s="10" t="s">
         <v>135</v>
@@ -9201,10 +9201,10 @@
         <v>35947</v>
       </c>
       <c r="G128" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H128" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I128" s="10" t="s">
         <v>135</v>
@@ -9233,10 +9233,10 @@
         <v>35947</v>
       </c>
       <c r="G129" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H129" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I129" s="10" t="s">
         <v>135</v>
@@ -9265,10 +9265,10 @@
         <v>35947</v>
       </c>
       <c r="G130" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H130" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I130" s="10" t="s">
         <v>135</v>
@@ -9297,10 +9297,10 @@
         <v>35947</v>
       </c>
       <c r="G131" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H131" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I131" s="10" t="s">
         <v>135</v>
@@ -9329,10 +9329,10 @@
         <v>35947</v>
       </c>
       <c r="G132" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H132" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I132" s="10" t="s">
         <v>135</v>
@@ -9361,10 +9361,10 @@
         <v>35947</v>
       </c>
       <c r="G133" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H133" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I133" s="10" t="s">
         <v>135</v>
@@ -9393,10 +9393,10 @@
         <v>35947</v>
       </c>
       <c r="G134" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H134" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I134" s="10" t="s">
         <v>135</v>
@@ -9425,10 +9425,10 @@
         <v>35947</v>
       </c>
       <c r="G135" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H135" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I135" s="10" t="s">
         <v>135</v>
@@ -9457,10 +9457,10 @@
         <v>35947</v>
       </c>
       <c r="G136" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H136" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I136" s="10" t="s">
         <v>135</v>
@@ -9489,10 +9489,10 @@
         <v>35947</v>
       </c>
       <c r="G137" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H137" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I137" s="10" t="s">
         <v>135</v>
@@ -9653,7 +9653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DW36"/>
+  <dimension ref="A1:DW38"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -12342,382 +12342,382 @@
         <v>132</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="T8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="U8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="V8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="W8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="X8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Y8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Z8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AX8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AY8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="AZ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BX8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BY8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="BZ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CX8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CY8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="CZ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DA8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DB8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DC8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DD8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DE8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DF8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DG8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DH8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DI8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DJ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DK8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DL8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DM8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DN8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DO8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DP8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DQ8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DR8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DS8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DT8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DU8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DV8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="DW8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="9" spans="1:127" x14ac:dyDescent="0.2">
@@ -12725,382 +12725,382 @@
         <v>133</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="X9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AZ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BX9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BZ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CX9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CY9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CZ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DA9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DB9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DC9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DD9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DE9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DF9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DG9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DH9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DI9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DJ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DK9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DL9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DM9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DN9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DO9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DP9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DQ9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DR9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DS9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DT9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DU9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DV9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="DW9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:127" x14ac:dyDescent="0.2">
@@ -23442,6 +23442,772 @@
       </c>
       <c r="DW36" s="8">
         <v>142.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B37" s="8">
+        <v>149</v>
+      </c>
+      <c r="C37" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="D37" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="E37" s="8">
+        <v>149</v>
+      </c>
+      <c r="F37" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="G37" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="H37" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="I37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="J37" s="8">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="K37" s="8">
+        <v>149</v>
+      </c>
+      <c r="L37" s="8">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="M37" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="N37" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="O37" s="8">
+        <v>149</v>
+      </c>
+      <c r="P37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>148.5</v>
+      </c>
+      <c r="R37" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="S37" s="8">
+        <v>149</v>
+      </c>
+      <c r="T37" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="U37" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="V37" s="8">
+        <v>153</v>
+      </c>
+      <c r="W37" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="X37" s="8">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="Y37" s="8">
+        <v>150</v>
+      </c>
+      <c r="Z37" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="AA37" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="AB37" s="8">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="AC37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AD37" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="AE37" s="8">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="AF37" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="AG37" s="8">
+        <v>148</v>
+      </c>
+      <c r="AH37" s="8">
+        <v>145.1</v>
+      </c>
+      <c r="AI37" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="AJ37" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="AK37" s="8">
+        <v>143</v>
+      </c>
+      <c r="AL37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="AM37" s="8">
+        <v>143</v>
+      </c>
+      <c r="AN37" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="AO37" s="8">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="AP37" s="8">
+        <v>150</v>
+      </c>
+      <c r="AQ37" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="AR37" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="AS37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="AT37" s="8">
+        <v>147.5</v>
+      </c>
+      <c r="AU37" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="AV37" s="8">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="AW37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="AX37" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="AY37" s="8">
+        <v>151.6</v>
+      </c>
+      <c r="AZ37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="BA37" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="BB37" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="BC37" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="BD37" s="8">
+        <v>148</v>
+      </c>
+      <c r="BE37" s="8">
+        <v>145.1</v>
+      </c>
+      <c r="BF37" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="BG37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="BH37" s="8">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="BI37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="BJ37" s="8">
+        <v>143.5</v>
+      </c>
+      <c r="BK37" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="BL37" s="8">
+        <v>143.5</v>
+      </c>
+      <c r="BM37" s="8">
+        <v>149</v>
+      </c>
+      <c r="BN37" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="BO37" s="8">
+        <v>156</v>
+      </c>
+      <c r="BP37" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="BQ37" s="8">
+        <v>147.6</v>
+      </c>
+      <c r="BR37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="BS37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="BT37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="BU37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="BV37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="BW37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="BX37" s="8">
+        <v>149</v>
+      </c>
+      <c r="BY37" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="BZ37" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="CA37" s="8">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="CB37" s="8">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="CC37" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="CD37" s="8">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="CE37" s="8">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="CF37" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="CG37" s="8">
+        <v>149</v>
+      </c>
+      <c r="CH37" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="CI37" s="8">
+        <v>157.5</v>
+      </c>
+      <c r="CJ37" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="CK37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="CL37" s="8">
+        <v>145.1</v>
+      </c>
+      <c r="CM37" s="8">
+        <v>146.5</v>
+      </c>
+      <c r="CN37" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="CO37" s="8">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="CP37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="CQ37" s="8">
+        <v>143</v>
+      </c>
+      <c r="CR37" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="CS37" s="8">
+        <v>143.5</v>
+      </c>
+      <c r="CT37" s="8">
+        <v>149.80000000000001</v>
+      </c>
+      <c r="CU37" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="CV37" s="8">
+        <v>159.30000000000001</v>
+      </c>
+      <c r="CW37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="CX37" s="8">
+        <v>147.30000000000001</v>
+      </c>
+      <c r="CY37" s="8">
+        <v>149</v>
+      </c>
+      <c r="CZ37" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="DA37" s="8">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="DB37" s="8">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="DC37" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="DD37" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="DE37" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="DF37" s="8">
+        <v>149</v>
+      </c>
+      <c r="DG37" s="8">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="DH37" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="DI37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="DJ37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="DK37" s="8">
+        <v>145</v>
+      </c>
+      <c r="DL37" s="8">
+        <v>146.6</v>
+      </c>
+      <c r="DM37" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="DN37" s="8">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="DO37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="DP37" s="8">
+        <v>143.4</v>
+      </c>
+      <c r="DQ37" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="DR37" s="8">
+        <v>143.69999999999999</v>
+      </c>
+      <c r="DS37" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="DT37" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="DU37" s="8">
+        <v>156</v>
+      </c>
+      <c r="DV37" s="8">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="DW37" s="8">
+        <v>147.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B38" s="8">
+        <v>154</v>
+      </c>
+      <c r="C38" s="8">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="D38" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="F38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="G38" s="8">
+        <v>156</v>
+      </c>
+      <c r="H38" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="I38" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="J38" s="8">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="K38" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="L38" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="M38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="N38" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="O38" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="P38" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="R38" s="8">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="S38" s="8">
+        <v>154</v>
+      </c>
+      <c r="T38" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="U38" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="V38" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="W38" s="8">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="X38" s="8">
+        <v>150.9</v>
+      </c>
+      <c r="Y38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="Z38" s="8">
+        <v>156.4</v>
+      </c>
+      <c r="AA38" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="AB38" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="AC38" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AD38" s="8">
+        <v>155.9</v>
+      </c>
+      <c r="AE38" s="8">
+        <v>163.1</v>
+      </c>
+      <c r="AF38" s="8">
+        <v>153.69999999999999</v>
+      </c>
+      <c r="AG38" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="AH38" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="AI38" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="AJ38" s="8">
+        <v>153.5</v>
+      </c>
+      <c r="AK38" s="8">
+        <v>148</v>
+      </c>
+      <c r="AL38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="AM38" s="8">
+        <v>147.69999999999999</v>
+      </c>
+      <c r="AN38" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="AO38" s="8">
+        <v>148.30000000000001</v>
+      </c>
+      <c r="AP38" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="AQ38" s="8">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="AR38" s="8">
+        <v>165.8</v>
+      </c>
+      <c r="AS38" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="AT38" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="AU38" s="8">
+        <v>164.6</v>
+      </c>
+      <c r="AV38" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="AW38" s="8">
+        <v>154</v>
+      </c>
+      <c r="AX38" s="8">
+        <v>160.19999999999999</v>
+      </c>
+      <c r="AY38" s="8">
+        <v>155.9</v>
+      </c>
+      <c r="AZ38" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="BA38" s="8">
+        <v>155.9</v>
+      </c>
+      <c r="BB38" s="8">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="BC38" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="BD38" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="BE38" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="BF38" s="8">
+        <v>151.6</v>
+      </c>
+      <c r="BG38" s="8">
+        <v>154.4</v>
+      </c>
+      <c r="BH38" s="8">
+        <v>148.69999999999999</v>
+      </c>
+      <c r="BI38" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="BJ38" s="8">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="BK38" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="BL38" s="8">
+        <v>148.5</v>
+      </c>
+      <c r="BM38" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="BN38" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="BO38" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="BP38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="BQ38" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="BR38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="BS38" s="8">
+        <v>156.4</v>
+      </c>
+      <c r="BT38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="BU38" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="BV38" s="8">
+        <v>156.5</v>
+      </c>
+      <c r="BW38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="BX38" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="BY38" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="BZ38" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="CA38" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="CB38" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="CC38" s="8">
+        <v>158.6</v>
+      </c>
+      <c r="CD38" s="8">
+        <v>154.1</v>
+      </c>
+      <c r="CE38" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="CF38" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="CG38" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="CH38" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="CI38" s="8">
+        <v>163.4</v>
+      </c>
+      <c r="CJ38" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="CK38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="CL38" s="8">
+        <v>149.6</v>
+      </c>
+      <c r="CM38" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="CN38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="CO38" s="8">
+        <v>147.80000000000001</v>
+      </c>
+      <c r="CP38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="CQ38" s="8">
+        <v>147.6</v>
+      </c>
+      <c r="CR38" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="CS38" s="8">
+        <v>148.4</v>
+      </c>
+      <c r="CT38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="CU38" s="8">
+        <v>160.4</v>
+      </c>
+      <c r="CV38" s="8">
+        <v>165.8</v>
+      </c>
+      <c r="CW38" s="8">
+        <v>155.6</v>
+      </c>
+      <c r="CX38" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="CY38" s="8">
+        <v>154</v>
+      </c>
+      <c r="CZ38" s="8">
+        <v>164.4</v>
+      </c>
+      <c r="DA38" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="DB38" s="8">
+        <v>153.80000000000001</v>
+      </c>
+      <c r="DC38" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="DD38" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="DE38" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="DF38" s="8">
+        <v>154.30000000000001</v>
+      </c>
+      <c r="DG38" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="DH38" s="8">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="DI38" s="8">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="DJ38" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="DK38" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="DL38" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="DM38" s="8">
+        <v>154</v>
+      </c>
+      <c r="DN38" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="DO38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="DP38" s="8">
+        <v>148.1</v>
+      </c>
+      <c r="DQ38" s="8">
+        <v>152.69999999999999</v>
+      </c>
+      <c r="DR38" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="DS38" s="8">
+        <v>153.9</v>
+      </c>
+      <c r="DT38" s="8">
+        <v>160.1</v>
+      </c>
+      <c r="DU38" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="DV38" s="8">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="DW38" s="8">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
